--- a/Database/Mentor_Hub.xlsx
+++ b/Database/Mentor_Hub.xlsx
@@ -5990,11 +5990,11 @@
           <t>Corroded Iron, cracked glass, Kintsugi gold, toxic amber bioluminescence</t>
         </is>
       </c>
-      <c r="F162" s="5" t="n">
-        <v>46138.92338092592</v>
+      <c r="F162" s="6" t="n">
+        <v>46141.66830168982</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H162" s="2" t="n"/>
     </row>
@@ -6670,11 +6670,11 @@
           <t>Obsidian, Starlight Jade, crystalline charts, stardust</t>
         </is>
       </c>
-      <c r="F182" s="5" t="n">
-        <v>46138.9239622801</v>
+      <c r="F182" s="6" t="n">
+        <v>46141.66572591435</v>
       </c>
       <c r="G182" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" s="2" t="n"/>
     </row>
@@ -6704,11 +6704,11 @@
           <t>Brass, Amber, crystalline charts, golden stardust</t>
         </is>
       </c>
-      <c r="F183" s="5" t="n">
-        <v>46138.92398402778</v>
+      <c r="F183" s="6" t="n">
+        <v>46141.66674166667</v>
       </c>
       <c r="G183" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H183" s="2" t="n"/>
     </row>
@@ -6738,11 +6738,11 @@
           <t>Moonstone, Imperial Jade, talisman fragments, ink-wash nebula</t>
         </is>
       </c>
-      <c r="F184" s="5" t="n">
-        <v>46138.92401115741</v>
+      <c r="F184" s="6" t="n">
+        <v>46141.66862887731</v>
       </c>
       <c r="G184" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H184" s="2" t="n"/>
     </row>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="F219" s="6" t="n">
-        <v>46140.63219750221</v>
+        <v>46140.6321975</v>
       </c>
       <c r="G219" s="4" t="n">
         <v>1</v>
@@ -10070,11 +10070,11 @@
           <t>Imperial Green Jade, Moonstone, Floating Obsidian, Talisman Fragments</t>
         </is>
       </c>
-      <c r="F282" s="5" t="n">
-        <v>46138.93626802084</v>
+      <c r="F282" s="6" t="n">
+        <v>46141.66742349537</v>
       </c>
       <c r="G282" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H282" s="2" t="n"/>
     </row>
@@ -10104,11 +10104,11 @@
           <t>Imperial Green Jade, Floating Obsidian, Amethyst, Crystalline Water</t>
         </is>
       </c>
-      <c r="F283" s="5" t="n">
-        <v>46138.93628987268</v>
+      <c r="F283" s="6" t="n">
+        <v>46141.66767443287</v>
       </c>
       <c r="G283" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H283" s="2" t="n"/>
     </row>
@@ -12110,11 +12110,11 @@
           <t>Moonstone, Imperial Jade, Aquamarine, Brushed Metal, Clockwork Brass</t>
         </is>
       </c>
-      <c r="F342" s="5" t="n">
-        <v>46138.94156866898</v>
+      <c r="F342" s="6" t="n">
+        <v>46141.66895539352</v>
       </c>
       <c r="G342" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H342" s="2" t="n"/>
     </row>
@@ -18910,11 +18910,11 @@
           <t>Cyanotype Paper, Silver Ink, Moonstone, Imperial Jade, Archival Stock</t>
         </is>
       </c>
-      <c r="F542" s="5" t="n">
-        <v>46138.95090752315</v>
+      <c r="F542" s="6" t="n">
+        <v>46141.66722292824</v>
       </c>
       <c r="G542" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H542" s="2" t="n"/>
     </row>
@@ -20270,11 +20270,11 @@
           <t>Rough Raku Pottery, Moonstone, Imperial Jade, Emerald Steam, Ink-Wash Nebula</t>
         </is>
       </c>
-      <c r="F582" s="5" t="n">
-        <v>46138.95255313657</v>
+      <c r="F582" s="6" t="n">
+        <v>46141.66921563658</v>
       </c>
       <c r="G582" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H582" s="2" t="n"/>
     </row>
@@ -20304,11 +20304,11 @@
           <t>Rough Raku Pottery, Burnt Sienna, Emerald Steam, Amber Light</t>
         </is>
       </c>
-      <c r="F583" s="5" t="n">
-        <v>46138.9525803588</v>
+      <c r="F583" s="6" t="n">
+        <v>46141.6695459756</v>
       </c>
       <c r="G583" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H583" s="2" t="n"/>
     </row>
@@ -20950,11 +20950,11 @@
           <t>Hand-blown Glass, Moonstone Glass, Imperial Jade, Copper Wire, Talisman Paper, Ink-wash Etching</t>
         </is>
       </c>
-      <c r="F602" s="5" t="n">
-        <v>46138.95327587963</v>
+      <c r="F602" s="6" t="n">
+        <v>46141.66799193287</v>
       </c>
       <c r="G602" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H602" s="2" t="n"/>
     </row>
